--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -51,27 +51,228 @@
   </si>
   <si>
     <t>效果名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>效果描述</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>效果id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>peedUp</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>加速</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(list#sep=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>),int</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述用tag</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>grantedTags</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff生效时，获得的tag</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>assetTags</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>applicationRequiredTags</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ongoingRequiredTags</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用需求tag</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeGameplayEffectsWithTags</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>激活需求tag</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除持有这些tag的buff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>immunityTags</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>免疫的tag</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续时间</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>period</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>间隔</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>periodEffect</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>间隔执行的Buff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>timeUnit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间单位：0=帧，1=回合</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>modifiers</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性数值修改器</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cueOnApply</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用时触发的cue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cueOnTick</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>伴随buff的持续cue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cueOnAdd</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cueOnRemove</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加时触发的cue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除时触发的cue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cueOnActivate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>激活时触发的cue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cueOnDeactivate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>失活时触发的cue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -97,6 +298,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -117,19 +324,26 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -413,20 +627,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="14.125" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="19.125" customWidth="1"/>
-    <col min="8" max="8" width="23.25" customWidth="1"/>
-    <col min="9" max="9" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="9.875" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
     <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="9.25" customWidth="1"/>
+    <col min="21" max="21" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,10 +655,59 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -455,88 +720,197 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="C7" s="1"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="1"/>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="2"/>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="1"/>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -562,24 +936,29 @@
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="2"/>
+      <c r="B21" s="1"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="1"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="2"/>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="1"/>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE80504E-4A22-446E-9C82-3254F107261D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -254,11 +255,43 @@
     <t>失活时触发的cue</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>buff赋予的能力</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>grantedAbility#format=lua</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,grantedAbility</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking#format=lua</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff堆叠</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001 , 1002</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -328,7 +361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -346,10 +379,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -626,23 +672,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W27"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="9.875" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="11" width="9.25" customWidth="1"/>
-    <col min="21" max="21" width="16.75" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" customWidth="1"/>
+    <col min="21" max="21" width="16.77734375" customWidth="1"/>
+    <col min="22" max="22" width="26.77734375" customWidth="1"/>
+    <col min="23" max="23" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,8 +754,14 @@
       <c r="U1" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -769,10 +823,16 @@
         <v>13</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -782,7 +842,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -846,115 +906,139 @@
       <c r="U4" s="6" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="V4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="E5" s="7">
+        <v>1001</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="9">
+        <v>500</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="W5" s="6"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" s="1"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE80504E-4A22-446E-9C82-3254F107261D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -52,15 +51,15 @@
   </si>
   <si>
     <t>效果名</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>效果描述</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>效果id</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -77,11 +76,11 @@
       </rPr>
       <t>peedUp</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>加速</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -109,195 +108,225 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>描述用tag</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>grantedTags</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>buff生效时，获得的tag</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>assetTags</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>applicationRequiredTags</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ongoingRequiredTags</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>应用需求tag</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>removeGameplayEffectsWithTags</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>激活需求tag</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>移除持有这些tag的buff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>immunityTags</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>免疫的tag</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>duration</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>持续时间</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>period</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>间隔</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>periodEffect</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>间隔执行的Buff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>timeUnit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>时间单位：0=帧，1=回合</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>modifiers</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>属性数值修改器</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cueOnApply</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>应用时触发的cue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cueOnTick</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>伴随buff的持续cue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cueOnAdd</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cueOnRemove</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>添加时触发的cue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>移除时触发的cue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cueOnActivate</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>激活时触发的cue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>cueOnDeactivate</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>失活时触发的cue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>buff赋予的能力</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=,),int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>grantedAbility#format=lua</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>list,grantedAbility</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>stacking#format=lua</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>buff堆叠</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>1001 , 1002</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>stacking?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>grantedAbility#format=json</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>stacking#format=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>json</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>间隔执行逻辑</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>period</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -357,45 +386,51 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -672,25 +707,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V26"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="4" max="4" width="9.875" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" customWidth="1"/>
-    <col min="11" max="11" width="9.21875" customWidth="1"/>
-    <col min="21" max="21" width="16.77734375" customWidth="1"/>
-    <col min="22" max="22" width="26.77734375" customWidth="1"/>
-    <col min="23" max="23" width="18.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="9.25" customWidth="1"/>
+    <col min="20" max="20" width="16.75" customWidth="1"/>
+    <col min="21" max="21" width="26.75" customWidth="1"/>
+    <col min="22" max="22" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -722,7 +757,7 @@
         <v>24</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>26</v>
@@ -731,37 +766,34 @@
         <v>29</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>43</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="W1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="V1" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -793,13 +825,13 @@
         <v>13</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>27</v>
+      <c r="M2" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>13</v>
@@ -820,229 +852,212 @@
         <v>13</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1001</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="7">
-        <v>1001</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="G4" s="9">
         <v>500</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="W5" s="6"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="V4" s="6"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C7" s="1"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="1"/>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="1"/>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58208A2-1209-4533-BD5D-E7F54823EE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -259,10 +260,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>1001 , 1002</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>stacking?</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -308,11 +305,15 @@
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>1001 ,1002</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -418,19 +419,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -707,25 +708,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="9.875" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="11" width="9.25" customWidth="1"/>
-    <col min="20" max="20" width="16.75" customWidth="1"/>
-    <col min="21" max="21" width="26.75" customWidth="1"/>
-    <col min="22" max="22" width="18.875" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" customWidth="1"/>
+    <col min="20" max="20" width="16.77734375" customWidth="1"/>
+    <col min="21" max="21" width="26.77734375" customWidth="1"/>
+    <col min="22" max="22" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,14 +787,14 @@
       <c r="T1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="V1" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -830,8 +831,8 @@
       <c r="L2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="12" t="s">
-        <v>56</v>
+      <c r="M2" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>13</v>
@@ -858,10 +859,10 @@
         <v>49</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -898,8 +899,8 @@
       <c r="L3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="13" t="s">
-        <v>55</v>
+      <c r="M3" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>34</v>
@@ -929,7 +930,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7">
         <v>1001</v>
@@ -943,8 +944,8 @@
       <c r="E4" s="7">
         <v>1001</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>51</v>
+      <c r="F4" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="G4" s="9">
         <v>500</v>
@@ -961,99 +962,99 @@
       <c r="Q4" s="10"/>
       <c r="V4" s="6"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58208A2-1209-4533-BD5D-E7F54823EE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FE0FFB-9973-4D65-BAA3-7F3F9B2E9675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,34 +84,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>(list#sep=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>),int</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>描述用tag</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -245,10 +217,6 @@
   </si>
   <si>
     <t>buff赋予的能力</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -306,7 +274,28 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>1001 ,1002</t>
+    <r>
+      <t>(list#sep=;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>),int</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001;1002</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=;),int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -740,58 +729,58 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="S1" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V1" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -807,59 +796,59 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
+      <c r="E2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -876,58 +865,58 @@
         <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="J3" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="S3" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="V3" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -945,7 +934,7 @@
         <v>1001</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="9">
         <v>500</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FE0FFB-9973-4D65-BAA3-7F3F9B2E9675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9A675A-DD66-4272-B8F7-AD6198D8A210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,74 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>fangmenglu</author>
+  </authors>
+  <commentList>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{EF9D0ED3-5AED-4584-98F4-4714D3E5DCE6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>ex-hard:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+buff生效时，获得的tag
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{DDFA6429-6E2C-4C91-AD31-B009E1F1E9A4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">ex-hard:
+0 = 帧
+1 = 回合
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -92,10 +158,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>buff生效时，获得的tag</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>assetTags</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -136,10 +198,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>持续时间</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -148,18 +206,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>timeUnit</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间单位：0=帧，1=回合</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>modifiers</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -220,40 +266,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>list,grantedAbility</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>buff堆叠</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>stacking?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>grantedAbility#format=json</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>stacking#format=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>json</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>间隔执行逻辑</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -298,12 +311,80 @@
     <t>(list#sep=;),int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>duration?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间单位</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>grantedAbility</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行GE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>间隔时间</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否起始触发</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=|),grantedAbility</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆叠代码</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆叠类型</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续时间刷新策略</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>间隔重置策略</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>过期策略</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>溢出刷新持续时间</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>溢出清除层数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆叠层数上限</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>溢出触发GE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,6 +437,21 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -380,7 +476,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -404,9 +500,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
@@ -416,6 +509,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -697,25 +808,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" customWidth="1"/>
-    <col min="11" max="11" width="9.21875" customWidth="1"/>
-    <col min="20" max="20" width="16.77734375" customWidth="1"/>
-    <col min="21" max="21" width="26.77734375" customWidth="1"/>
-    <col min="22" max="22" width="18.88671875" customWidth="1"/>
+    <col min="3" max="4" width="12.21875" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="25.77734375" customWidth="1"/>
+    <col min="8" max="8" width="24.88671875" customWidth="1"/>
+    <col min="9" max="9" width="37" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" customWidth="1"/>
+    <col min="13" max="15" width="14.21875" customWidth="1"/>
+    <col min="16" max="16" width="15.21875" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" customWidth="1"/>
+    <col min="19" max="19" width="13.44140625" customWidth="1"/>
+    <col min="20" max="20" width="15.21875" customWidth="1"/>
+    <col min="21" max="21" width="17.77734375" customWidth="1"/>
+    <col min="22" max="22" width="18.6640625" customWidth="1"/>
+    <col min="23" max="23" width="24.5546875" customWidth="1"/>
+    <col min="24" max="24" width="12.21875" customWidth="1"/>
+    <col min="25" max="25" width="11" customWidth="1"/>
+    <col min="26" max="26" width="14.77734375" customWidth="1"/>
+    <col min="27" max="27" width="19.5546875" customWidth="1"/>
+    <col min="28" max="28" width="15.5546875" customWidth="1"/>
+    <col min="29" max="29" width="12.21875" customWidth="1"/>
+    <col min="30" max="30" width="17.33203125" customWidth="1"/>
+    <col min="31" max="31" width="14.33203125" customWidth="1"/>
+    <col min="32" max="32" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,61 +855,69 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="5" t="s">
+      <c r="U1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U1" s="11" t="s">
+      <c r="W1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="X1" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="V1" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -796,62 +930,70 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="13"/>
+      <c r="M2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -867,59 +1009,87 @@
       <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="J3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="6" t="s">
+      <c r="N3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="6" t="s">
+      <c r="T3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="W3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF3" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7">
         <v>1001</v>
@@ -930,81 +1100,83 @@
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="18">
         <v>1001</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="9">
+      <c r="F4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="17">
         <v>500</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="V4" s="6"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="X4" s="6"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1047,8 +1219,17 @@
       <c r="B26" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="X2:AF2"/>
+    <mergeCell ref="X1:AF1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="M1:O1"/>
+  </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9A675A-DD66-4272-B8F7-AD6198D8A210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0D7AF0-B62C-402A-A9FE-C89C3E7911F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -377,6 +377,14 @@
   </si>
   <si>
     <t>溢出触发GE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001;1002;1003</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;1;1;1;1|1;2;1;1;1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -510,6 +518,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -518,15 +535,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -860,7 +868,7 @@
       <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H1" s="5" t="s">
@@ -872,15 +880,15 @@
       <c r="J1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15" t="s">
+      <c r="L1" s="18"/>
+      <c r="M1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
       <c r="P1" s="5" t="s">
         <v>27</v>
       </c>
@@ -905,17 +913,17 @@
       <c r="W1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -940,7 +948,7 @@
         <v>44</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>44</v>
@@ -948,15 +956,15 @@
       <c r="J2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="13"/>
-      <c r="M2" s="14" t="s">
+      <c r="L2" s="16"/>
+      <c r="M2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
       <c r="P2" s="10" t="s">
         <v>44</v>
       </c>
@@ -981,17 +989,17 @@
       <c r="W2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="13"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1100,13 +1108,13 @@
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="15">
         <v>1001</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="14">
         <v>500</v>
       </c>
       <c r="H4" s="9"/>
@@ -1114,14 +1122,49 @@
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
+      <c r="M4" s="9">
+        <v>1</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="9" t="b">
+        <v>1</v>
+      </c>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
-      <c r="X4" s="6"/>
+      <c r="W4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0D7AF0-B62C-402A-A9FE-C89C3E7911F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,12 +24,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>fangmenglu</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{EF9D0ED3-5AED-4584-98F4-4714D3E5DCE6}">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{DDFA6429-6E2C-4C91-AD31-B009E1F1E9A4}">
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -118,15 +117,15 @@
   </si>
   <si>
     <t>效果名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>效果描述</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>效果id</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -143,131 +142,131 @@
       </rPr>
       <t>peedUp</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>加速</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>描述用tag</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>grantedTags</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>assetTags</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>applicationRequiredTags</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ongoingRequiredTags</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>应用需求tag</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>removeGameplayEffectsWithTags</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>激活需求tag</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>移除持有这些tag的buff</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>immunityTags</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>免疫的tag</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>duration</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>持续时间</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>period</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>modifiers</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>属性数值修改器</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>cueOnApply</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>应用时触发的cue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>cueOnTick</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>伴随buff的持续cue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>cueOnAdd</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>cueOnRemove</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>添加时触发的cue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>移除时触发的cue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>cueOnActivate</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>激活时触发的cue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>cueOnDeactivate</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>失活时触发的cue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>buff赋予的能力</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>stacking?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -284,7 +283,7 @@
       </rPr>
       <t>?</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -301,103 +300,128 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>1001;1002</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=;),int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>duration?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>时间单位</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>grantedAbility</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>stacking</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>执行GE</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>间隔时间</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>是否起始触发</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=|),grantedAbility</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>堆叠代码</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>堆叠类型</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>持续时间刷新策略</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>间隔重置策略</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>过期策略</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>溢出刷新持续时间</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>溢出清除层数</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>堆叠层数上限</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>溢出触发GE</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>1001;1002;1003</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>1;1;1;1;1|1;2;1;1;1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(list#sep=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>|),modifier</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -480,66 +504,69 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -816,40 +843,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AF26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="12.21875" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="25.77734375" customWidth="1"/>
-    <col min="8" max="8" width="24.88671875" customWidth="1"/>
+    <col min="3" max="4" width="12.25" customWidth="1"/>
+    <col min="5" max="5" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
+    <col min="8" max="8" width="24.875" customWidth="1"/>
     <col min="9" max="9" width="37" customWidth="1"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" customWidth="1"/>
-    <col min="13" max="15" width="14.21875" customWidth="1"/>
-    <col min="16" max="16" width="15.21875" customWidth="1"/>
+    <col min="10" max="10" width="18.875" customWidth="1"/>
+    <col min="11" max="11" width="12.25" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="15" width="14.25" customWidth="1"/>
+    <col min="16" max="16" width="15.25" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="15.109375" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" customWidth="1"/>
-    <col min="20" max="20" width="15.21875" customWidth="1"/>
-    <col min="21" max="21" width="17.77734375" customWidth="1"/>
-    <col min="22" max="22" width="18.6640625" customWidth="1"/>
-    <col min="23" max="23" width="24.5546875" customWidth="1"/>
-    <col min="24" max="24" width="12.21875" customWidth="1"/>
+    <col min="18" max="18" width="15.125" customWidth="1"/>
+    <col min="19" max="19" width="13.5" customWidth="1"/>
+    <col min="20" max="20" width="15.25" customWidth="1"/>
+    <col min="21" max="21" width="17.75" customWidth="1"/>
+    <col min="22" max="22" width="18.625" customWidth="1"/>
+    <col min="23" max="23" width="24.5" customWidth="1"/>
+    <col min="24" max="24" width="12.25" customWidth="1"/>
     <col min="25" max="25" width="11" customWidth="1"/>
-    <col min="26" max="26" width="14.77734375" customWidth="1"/>
-    <col min="27" max="27" width="19.5546875" customWidth="1"/>
-    <col min="28" max="28" width="15.5546875" customWidth="1"/>
-    <col min="29" max="29" width="12.21875" customWidth="1"/>
-    <col min="30" max="30" width="17.33203125" customWidth="1"/>
-    <col min="31" max="31" width="14.33203125" customWidth="1"/>
-    <col min="32" max="32" width="13.109375" customWidth="1"/>
+    <col min="26" max="26" width="14.75" customWidth="1"/>
+    <col min="27" max="27" width="19.5" customWidth="1"/>
+    <col min="28" max="28" width="15.5" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="30" max="30" width="17.375" customWidth="1"/>
+    <col min="31" max="31" width="14.375" customWidth="1"/>
+    <col min="32" max="32" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -925,7 +952,7 @@
       <c r="AE1" s="17"/>
       <c r="AF1" s="17"/>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -965,13 +992,13 @@
       </c>
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
-      <c r="P2" s="10" t="s">
-        <v>44</v>
+      <c r="P2" s="19" t="s">
+        <v>66</v>
       </c>
       <c r="Q2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="19" t="s">
         <v>44</v>
       </c>
       <c r="S2" s="10" t="s">
@@ -1001,7 +1028,7 @@
       <c r="AE2" s="16"/>
       <c r="AF2" s="16"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,7 +1124,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
       <c r="B4" s="7">
         <v>1001</v>
@@ -1166,99 +1193,99 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
@@ -1270,7 +1297,7 @@
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="M1:O1"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -331,6 +331,15 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>1002;200;2002;2003</t>
+  </si>
+  <si>
+    <t>2001;2002;2003</t>
+  </si>
+  <si>
+    <t>1;2;60;0;1001</t>
   </si>
 </sst>
 </file>
@@ -1053,20 +1062,22 @@
         <v>65</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>65</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="11" t="s">
+        <v>68</v>
+      </c>
       <c r="Q4" s="11" t="s">
         <v>65</v>
       </c>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -327,7 +327,7 @@
     <t>加速加速！！</t>
   </si>
   <si>
-    <t>1001</t>
+    <t>1001;1002;2001</t>
   </si>
   <si>
     <t/>
@@ -339,7 +339,7 @@
     <t>2001;2002;2003</t>
   </si>
   <si>
-    <t>1;2;60;0;1001</t>
+    <t>1;2;60;0;1001|1;3;50;3;1002</t>
   </si>
 </sst>
 </file>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BC2882-7F78-417A-891D-F49E5B712583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,12 +24,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>fangmenglu</author>
+    <author>大马鹿</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -86,12 +86,42 @@
         </r>
       </text>
     </comment>
+    <comment ref="Q3" authorId="1" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>EX-HARD:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+每组共5个参数：1.AttrSet属性集ID
+2.Attribute属性ID
+3.Magnitude基础模值
+4.Operation操作类型
+5.MMC计算逻辑【即exgas.mmc中的计算类型ID】</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -165,10 +195,10 @@
     <t>string</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>(list#sep=;</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -179,7 +209,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=;),int</t>
@@ -188,10 +218,10 @@
     <t>duration?</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>period</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -202,13 +232,13 @@
       </rPr>
       <t>?</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>(list#sep=</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -219,7 +249,7 @@
       </rPr>
       <t>|),modifier</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=|),grantedAbility</t>
@@ -270,9 +300,6 @@
     <t>是否起始触发</t>
   </si>
   <si>
-    <t>属性数值修改器</t>
-  </si>
-  <si>
     <t>应用时触发的cue</t>
   </si>
   <si>
@@ -340,19 +367,34 @@
   </si>
   <si>
     <t>1;2;60;0;1001|1;3;50;3;1002</t>
+  </si>
+  <si>
+    <t>激活时是否重置计时</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性数值修改器（每组共5个参数：1.AttrSet属性集ID；2.Attribute属性ID；3.Magnitude基础模值；4.Operation操作类型；5.MMC计算逻辑【即exgas.mmc中的计算类型ID】）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -396,6 +438,21 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -416,69 +473,68 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -760,40 +816,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AG26"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="12.21875" customWidth="1" style="3"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1" style="3"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1" style="3"/>
-    <col min="7" max="7" width="25.77734375" customWidth="1" style="3"/>
-    <col min="8" max="8" width="24.88671875" customWidth="1" style="3"/>
-    <col min="9" max="9" width="37" customWidth="1" style="3"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1" style="3"/>
-    <col min="11" max="11" width="12.21875" customWidth="1" style="3"/>
-    <col min="12" max="12" width="11.44140625" customWidth="1" style="3"/>
-    <col min="13" max="15" width="14.21875" customWidth="1" style="3"/>
-    <col min="16" max="16" width="15.21875" customWidth="1" style="3"/>
-    <col min="17" max="17" width="15" customWidth="1" style="3"/>
-    <col min="18" max="18" width="15.109375" customWidth="1" style="3"/>
-    <col min="19" max="19" width="13.44140625" customWidth="1" style="3"/>
-    <col min="20" max="20" width="15.21875" customWidth="1" style="3"/>
-    <col min="21" max="21" width="17.77734375" customWidth="1" style="3"/>
-    <col min="22" max="22" width="18.6640625" customWidth="1" style="3"/>
-    <col min="23" max="23" width="24.44140625" customWidth="1" style="3"/>
-    <col min="24" max="24" width="12.21875" customWidth="1" style="3"/>
-    <col min="25" max="25" width="11" customWidth="1" style="3"/>
-    <col min="26" max="26" width="14.77734375" customWidth="1" style="3"/>
-    <col min="27" max="27" width="19.44140625" customWidth="1" style="3"/>
-    <col min="28" max="28" width="15.44140625" customWidth="1" style="3"/>
-    <col min="29" max="29" width="12.21875" customWidth="1" style="3"/>
-    <col min="30" max="30" width="17.33203125" customWidth="1" style="3"/>
-    <col min="31" max="31" width="14.33203125" customWidth="1" style="3"/>
-    <col min="32" max="32" width="13.109375" customWidth="1" style="3"/>
+    <col min="3" max="4" width="12.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="37" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.25" style="10" customWidth="1"/>
+    <col min="13" max="13" width="21" style="2" customWidth="1"/>
+    <col min="14" max="16" width="14.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.25" style="2" customWidth="1"/>
+    <col min="18" max="18" width="15" style="2" customWidth="1"/>
+    <col min="19" max="19" width="15.125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="13.5" style="2" customWidth="1"/>
+    <col min="21" max="21" width="15.25" style="2" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="2" customWidth="1"/>
+    <col min="23" max="23" width="18.625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="24.5" style="2" customWidth="1"/>
+    <col min="25" max="25" width="12.25" style="2" customWidth="1"/>
+    <col min="26" max="26" width="11" style="2" customWidth="1"/>
+    <col min="27" max="27" width="14.75" style="2" customWidth="1"/>
+    <col min="28" max="28" width="19.5" style="2" customWidth="1"/>
+    <col min="29" max="29" width="15.5" style="2" customWidth="1"/>
+    <col min="30" max="30" width="12.25" style="2" customWidth="1"/>
+    <col min="31" max="31" width="17.375" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="13.125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2">
+    <row r="1" spans="1:33" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -806,61 +863,61 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="21" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="21"/>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="21"/>
+      <c r="N1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="21"/>
       <c r="O1" s="21"/>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="21"/>
+      <c r="Q1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="T1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="V1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="W1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="Y1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="20"/>
       <c r="Z1" s="20"/>
       <c r="AA1" s="20"/>
       <c r="AB1" s="20"/>
@@ -868,8 +925,9 @@
       <c r="AD1" s="20"/>
       <c r="AE1" s="20"/>
       <c r="AF1" s="20"/>
-    </row>
-    <row r="2">
+      <c r="AG1" s="20"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -882,61 +940,61 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="19"/>
-      <c r="M2" s="20" t="s">
+      <c r="L2" s="20"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="20"/>
       <c r="O2" s="20"/>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="20"/>
+      <c r="Q2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="R2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="S2" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="T2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="U2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="V2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="W2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="X2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="19" t="s">
+      <c r="Y2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="19"/>
       <c r="Z2" s="19"/>
       <c r="AA2" s="19"/>
       <c r="AB2" s="19"/>
@@ -944,277 +1002,272 @@
       <c r="AD2" s="19"/>
       <c r="AE2" s="19"/>
       <c r="AF2" s="19"/>
-    </row>
-    <row r="3">
+      <c r="AG2" s="19"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="O3" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="P3" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="S3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="T3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="U3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="V3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="W3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="X3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="Y3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="13" t="s">
+      <c r="Z3" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="AA3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="AB3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="13" t="s">
+      <c r="AC3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="13" t="s">
+      <c r="AD3" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AE3" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="AD3" s="13" t="s">
+      <c r="AF3" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AG3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="AF3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A4" s="8"/>
+      <c r="B4" s="16">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="17">
-        <v>1001</v>
-      </c>
-      <c r="C4" s="22" t="s">
+      <c r="D4" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="G4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="K4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="13"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-    </row>
-    <row r="5">
+      <c r="R4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="7"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells>
-    <mergeCell ref="X2:AF2"/>
-    <mergeCell ref="X1:AF1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="M1:O1"/>
+  <mergeCells count="6">
+    <mergeCell ref="Y2:AG2"/>
+    <mergeCell ref="Y1:AG1"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="N1:P1"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1,36 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DADB8FF-41F2-4366-B0F0-46AE5CE44173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>fangmenglu</author>
     <author>大马鹿</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -86,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="1" shapeId="0">
+    <comment ref="Q3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -195,10 +199,10 @@
     <t>string</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>(list#sep=;</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -209,7 +213,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=;),int</t>
@@ -218,10 +222,10 @@
     <t>duration?</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>period</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -232,13 +236,13 @@
       </rPr>
       <t>?</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>(list#sep=</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -249,7 +253,7 @@
       </rPr>
       <t>|),modifier</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=|),grantedAbility</t>
@@ -291,6 +295,9 @@
     <t>持续时间</t>
   </si>
   <si>
+    <t>激活时是否重置计时</t>
+  </si>
+  <si>
     <t>间隔时间</t>
   </si>
   <si>
@@ -300,6 +307,9 @@
     <t>是否起始触发</t>
   </si>
   <si>
+    <t>属性数值修改器（每组共5个参数：1.AttrSet属性集ID；2.Attribute属性ID；3.Magnitude基础模值；4.Operation操作类型；5.MMC计算逻辑【即exgas.mmc中的计算类型ID】）</t>
+  </si>
+  <si>
     <t>应用时触发的cue</t>
   </si>
   <si>
@@ -369,32 +379,29 @@
     <t>1;2;60;0;1001|1;3;50;3;1002</t>
   </si>
   <si>
-    <t>激活时是否重置计时</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性数值修改器（每组共5个参数：1.AttrSet属性集ID；2.Attribute属性ID；3.Magnitude基础模值；4.Operation操作类型；5.MMC计算逻辑【即exgas.mmc中的计算类型ID】）</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t>speed_up</t>
+  </si>
+  <si>
+    <t>加速buff</t>
+  </si>
+  <si>
+    <t>4001001</t>
+  </si>
+  <si>
+    <t>1;3;3;1;1001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -438,21 +445,6 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -473,67 +465,68 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="23">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -816,41 +809,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="12.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="24.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="37" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.25" style="10" customWidth="1"/>
-    <col min="13" max="13" width="21" style="2" customWidth="1"/>
-    <col min="14" max="16" width="14.25" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.25" style="2" customWidth="1"/>
-    <col min="18" max="18" width="15" style="2" customWidth="1"/>
-    <col min="19" max="19" width="15.125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="13.5" style="2" customWidth="1"/>
-    <col min="21" max="21" width="15.25" style="2" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="2" customWidth="1"/>
-    <col min="23" max="23" width="18.625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="24.5" style="2" customWidth="1"/>
-    <col min="25" max="25" width="12.25" style="2" customWidth="1"/>
-    <col min="26" max="26" width="11" style="2" customWidth="1"/>
-    <col min="27" max="27" width="14.75" style="2" customWidth="1"/>
-    <col min="28" max="28" width="19.5" style="2" customWidth="1"/>
-    <col min="29" max="29" width="15.5" style="2" customWidth="1"/>
-    <col min="30" max="30" width="12.25" style="2" customWidth="1"/>
-    <col min="31" max="31" width="17.375" style="2" customWidth="1"/>
-    <col min="32" max="32" width="14.375" style="2" customWidth="1"/>
-    <col min="33" max="33" width="13.125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.21875" customWidth="1" style="3"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1" style="3"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1" style="3"/>
+    <col min="7" max="7" width="25.77734375" customWidth="1" style="3"/>
+    <col min="8" max="8" width="24.88671875" customWidth="1" style="3"/>
+    <col min="9" max="9" width="37" customWidth="1" style="3"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1" style="3"/>
+    <col min="11" max="11" width="12.21875" customWidth="1" style="3"/>
+    <col min="12" max="12" width="12.21875" customWidth="1" style="11"/>
+    <col min="13" max="13" width="21" customWidth="1" style="3"/>
+    <col min="14" max="16" width="14.21875" customWidth="1" style="3"/>
+    <col min="17" max="17" width="15.21875" customWidth="1" style="3"/>
+    <col min="18" max="18" width="15" customWidth="1" style="3"/>
+    <col min="19" max="19" width="15.109375" customWidth="1" style="3"/>
+    <col min="20" max="20" width="13.44140625" customWidth="1" style="3"/>
+    <col min="21" max="21" width="15.21875" customWidth="1" style="3"/>
+    <col min="22" max="22" width="17.77734375" customWidth="1" style="3"/>
+    <col min="23" max="23" width="18.6640625" customWidth="1" style="3"/>
+    <col min="24" max="24" width="24.44140625" customWidth="1" style="3"/>
+    <col min="25" max="25" width="12.21875" customWidth="1" style="3"/>
+    <col min="26" max="26" width="11" customWidth="1" style="3"/>
+    <col min="27" max="27" width="14.77734375" customWidth="1" style="3"/>
+    <col min="28" max="28" width="19.44140625" customWidth="1" style="3"/>
+    <col min="29" max="29" width="15.44140625" customWidth="1" style="3"/>
+    <col min="30" max="30" width="12.21875" customWidth="1" style="3"/>
+    <col min="31" max="31" width="17.33203125" customWidth="1" style="3"/>
+    <col min="32" max="32" width="14.33203125" customWidth="1" style="3"/>
+    <col min="33" max="33" width="13.109375" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" ht="19.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,71 +856,71 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21" t="s">
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="6" t="s">
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="X1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Y1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="21"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21"/>
+      <c r="AF1" s="21"/>
+      <c r="AG1" s="21"/>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -940,324 +933,390 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="20"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="20" t="s">
+      <c r="L2" s="21"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="17" t="s">
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="R2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="V2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="X2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="Y2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="19"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC3" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD3" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE3" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG3" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9"/>
+      <c r="B4" s="17">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="N3" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="18" t="s">
+      <c r="K4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="R3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z3" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB3" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD3" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE3" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF3" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG3" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A4" s="8"/>
-      <c r="B4" s="16">
-        <v>1001</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="R4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="8"/>
+    </row>
+    <row r="5">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11">
+        <v>-1</v>
+      </c>
+      <c r="M5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+    </row>
+    <row r="6">
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="3"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25">
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells>
     <mergeCell ref="Y2:AG2"/>
     <mergeCell ref="Y1:AG1"/>
     <mergeCell ref="K2:M2"/>
@@ -1265,9 +1324,10 @@
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="N1:P1"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -358,25 +358,19 @@
     <t>溢出触发GE</t>
   </si>
   <si>
-    <t>加速测试a</t>
-  </si>
-  <si>
-    <t>加速加速！！</t>
-  </si>
-  <si>
-    <t>1001;1002;2001</t>
+    <t>测试受伤</t>
+  </si>
+  <si>
+    <t>受到2点伤害</t>
+  </si>
+  <si>
+    <t>3003</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>1002;200;2002;2003</t>
-  </si>
-  <si>
-    <t>2001;2002;2003</t>
-  </si>
-  <si>
-    <t>1;2;60;0;1001|1;3;50;3;1002</t>
+    <t>1;1;2;3;1001</t>
   </si>
   <si>
     <t>speed_up</t>
@@ -1117,21 +1111,22 @@
         <v>66</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>66</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R4" s="11" t="s">
         <v>66</v>
@@ -1153,6 +1148,14 @@
       </c>
       <c r="X4" s="13"/>
       <c r="Y4" s="8"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
@@ -1160,16 +1163,16 @@
         <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>66</v>
@@ -1196,7 +1199,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>66</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -383,6 +383,51 @@
   </si>
   <si>
     <t>1;3;3;1;1001</t>
+  </si>
+  <si>
+    <t>debug_effect1</t>
+  </si>
+  <si>
+    <t>调试用的测试ge</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>1;2;10;3;1002</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>debug_effect2</t>
+  </si>
+  <si>
+    <t>调试用测试GE</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>1;1;1;3;1001</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>False</t>
   </si>
 </sst>
 </file>
@@ -463,11 +508,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
@@ -807,34 +853,34 @@
   <dimension ref="A1:AG26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="12.21875" customWidth="1" style="3"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1" style="3"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1" style="3"/>
-    <col min="7" max="7" width="25.77734375" customWidth="1" style="3"/>
-    <col min="8" max="8" width="24.88671875" customWidth="1" style="3"/>
-    <col min="9" max="9" width="37" customWidth="1" style="3"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1" style="3"/>
-    <col min="11" max="11" width="12.21875" customWidth="1" style="3"/>
-    <col min="12" max="12" width="12.21875" customWidth="1" style="11"/>
-    <col min="13" max="13" width="21" customWidth="1" style="3"/>
-    <col min="14" max="16" width="14.21875" customWidth="1" style="3"/>
-    <col min="17" max="17" width="15.21875" customWidth="1" style="3"/>
-    <col min="18" max="18" width="15" customWidth="1" style="3"/>
-    <col min="19" max="19" width="15.109375" customWidth="1" style="3"/>
-    <col min="20" max="20" width="13.44140625" customWidth="1" style="3"/>
-    <col min="21" max="21" width="15.21875" customWidth="1" style="3"/>
-    <col min="22" max="22" width="17.77734375" customWidth="1" style="3"/>
-    <col min="23" max="23" width="18.6640625" customWidth="1" style="3"/>
-    <col min="24" max="24" width="24.44140625" customWidth="1" style="3"/>
-    <col min="25" max="25" width="12.21875" customWidth="1" style="3"/>
-    <col min="26" max="26" width="11" customWidth="1" style="3"/>
-    <col min="27" max="27" width="14.77734375" customWidth="1" style="3"/>
-    <col min="28" max="28" width="19.44140625" customWidth="1" style="3"/>
-    <col min="29" max="29" width="15.44140625" customWidth="1" style="3"/>
-    <col min="30" max="30" width="12.21875" customWidth="1" style="3"/>
-    <col min="31" max="31" width="17.33203125" customWidth="1" style="3"/>
-    <col min="32" max="32" width="14.33203125" customWidth="1" style="3"/>
-    <col min="33" max="33" width="13.109375" customWidth="1" style="3"/>
+    <col min="3" max="4" width="12.21875" customWidth="1" style="4"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1" style="4"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1" style="4"/>
+    <col min="7" max="7" width="25.77734375" customWidth="1" style="4"/>
+    <col min="8" max="8" width="24.88671875" customWidth="1" style="4"/>
+    <col min="9" max="9" width="37" customWidth="1" style="4"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1" style="4"/>
+    <col min="11" max="11" width="12.21875" customWidth="1" style="4"/>
+    <col min="12" max="12" width="12.21875" customWidth="1" style="12"/>
+    <col min="13" max="13" width="21" customWidth="1" style="4"/>
+    <col min="14" max="16" width="14.21875" customWidth="1" style="4"/>
+    <col min="17" max="17" width="15.21875" customWidth="1" style="4"/>
+    <col min="18" max="18" width="15" customWidth="1" style="4"/>
+    <col min="19" max="19" width="15.109375" customWidth="1" style="4"/>
+    <col min="20" max="20" width="13.44140625" customWidth="1" style="4"/>
+    <col min="21" max="21" width="15.21875" customWidth="1" style="4"/>
+    <col min="22" max="22" width="17.77734375" customWidth="1" style="4"/>
+    <col min="23" max="23" width="18.6640625" customWidth="1" style="4"/>
+    <col min="24" max="24" width="24.44140625" customWidth="1" style="4"/>
+    <col min="25" max="25" width="12.21875" customWidth="1" style="4"/>
+    <col min="26" max="26" width="11" customWidth="1" style="4"/>
+    <col min="27" max="27" width="14.77734375" customWidth="1" style="4"/>
+    <col min="28" max="28" width="19.44140625" customWidth="1" style="4"/>
+    <col min="29" max="29" width="15.44140625" customWidth="1" style="4"/>
+    <col min="30" max="30" width="12.21875" customWidth="1" style="4"/>
+    <col min="31" max="31" width="17.33203125" customWidth="1" style="4"/>
+    <col min="32" max="32" width="14.33203125" customWidth="1" style="4"/>
+    <col min="33" max="33" width="13.109375" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2">
@@ -850,69 +896,69 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22" t="s">
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="7" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="21" t="s">
+      <c r="Y1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="21"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="21"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="21"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -927,235 +973,235 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="21" t="s">
+      <c r="L2" s="22"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="18" t="s">
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="18" t="s">
+      <c r="S2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="Y2" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="Q3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="V3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="W3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="X3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Y3" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="Z3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="13" t="s">
+      <c r="AA3" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="13" t="s">
+      <c r="AB3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AC3" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="AD3" s="13" t="s">
+      <c r="AD3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AE3" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="AF3" s="13" t="s">
+      <c r="AF3" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AG3" s="13" t="s">
+      <c r="AG3" s="14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="17">
+      <c r="A4" s="10"/>
+      <c r="B4" s="18">
         <v>1001</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11" t="s">
+      <c r="F4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="R4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="T4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
+      <c r="R4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
@@ -1171,140 +1217,293 @@
       <c r="E5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" s="3">
+      <c r="G5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="4">
         <v>0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="12">
         <v>-1</v>
       </c>
-      <c r="M5" s="3" t="b">
+      <c r="M5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3" t="s">
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3"/>
+      <c r="R5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="4"/>
+      <c r="AG5" s="4"/>
     </row>
     <row r="6">
-      <c r="C6" s="1"/>
-      <c r="D6" s="4"/>
+      <c r="B6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
     </row>
     <row r="7">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="B7" s="5">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="12">
+        <v>600</v>
+      </c>
+      <c r="M7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>60</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="1"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9">
       <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10">
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11">
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
     </row>
     <row r="12">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
     </row>
     <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
     </row>
     <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
     </row>
     <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
     </row>
     <row r="21">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
     </row>
     <row r="22">
       <c r="B22" s="1"/>
@@ -1313,7 +1512,7 @@
       <c r="B23" s="1"/>
     </row>
     <row r="25">
-      <c r="B25" s="4"/>
+      <c r="B25" s="5"/>
     </row>
     <row r="26">
       <c r="B26" s="1"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -422,9 +422,6 @@
   </si>
   <si>
     <t>1;1;1;3;1001</t>
-  </si>
-  <si>
-    <t>1002</t>
   </si>
   <si>
     <t>False</t>
@@ -1407,7 +1404,7 @@
         <v>78</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="4">
@@ -1429,10 +1426,10 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>78</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -379,6 +379,9 @@
     <t>加速buff</t>
   </si>
   <si>
+    <t>4001001;3001</t>
+  </si>
+  <si>
     <t>4001001</t>
   </si>
   <si>
@@ -413,9 +416,6 @@
   </si>
   <si>
     <t>200</t>
-  </si>
-  <si>
-    <t>100</t>
   </si>
   <si>
     <t>True</t>
@@ -1215,7 +1215,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>66</v>
@@ -1242,7 +1242,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>66</v>
@@ -1278,28 +1278,28 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="J6" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="12"/>
@@ -1308,10 +1308,10 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S6" s="4" t="s">
         <v>66</v>
@@ -1344,16 +1344,16 @@
         <v>1005</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>66</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>66</v>
@@ -1380,7 +1380,7 @@
         <v>60</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>83</v>
@@ -1392,19 +1392,19 @@
         <v>66</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="4">
@@ -1432,7 +1432,7 @@
         <v>85</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>调试用测试GE</t>
+  </si>
+  <si>
+    <t>2006</t>
   </si>
   <si>
     <t>200</t>
@@ -1359,7 +1362,7 @@
         <v>66</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>66</v>
@@ -1383,10 +1386,10 @@
         <v>79</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>66</v>
@@ -1426,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>79</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -379,10 +379,7 @@
     <t>加速buff</t>
   </si>
   <si>
-    <t>4001001;3001</t>
-  </si>
-  <si>
-    <t>4001001</t>
+    <t>3001</t>
   </si>
   <si>
     <t>1;3;3;1;1001</t>
@@ -392,9 +389,6 @@
   </si>
   <si>
     <t>调试用的测试ge</t>
-  </si>
-  <si>
-    <t>3001</t>
   </si>
   <si>
     <t>400</t>
@@ -1218,7 +1212,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>66</v>
@@ -1245,7 +1239,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>66</v>
@@ -1281,28 +1275,28 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="H6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="12"/>
@@ -1311,10 +1305,10 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="S6" s="4" t="s">
         <v>66</v>
@@ -1347,22 +1341,22 @@
         <v>1005</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="G7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>66</v>
@@ -1383,31 +1377,31 @@
         <v>60</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>66</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="4">
@@ -1429,13 +1423,13 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -358,19 +358,19 @@
     <t>溢出触发GE</t>
   </si>
   <si>
-    <t>测试受伤</t>
-  </si>
-  <si>
-    <t>受到2点伤害</t>
-  </si>
-  <si>
-    <t>3003</t>
+    <t>奔跑耐力消耗</t>
+  </si>
+  <si>
+    <t>耐力减少2点/5帧</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>1;1;2;3;1001</t>
+    <t>9001</t>
+  </si>
+  <si>
+    <t>True</t>
   </si>
   <si>
     <t>speed_up</t>
@@ -415,13 +415,16 @@
     <t>200</t>
   </si>
   <si>
-    <t>True</t>
-  </si>
-  <si>
     <t>1;1;1;3;1001</t>
   </si>
   <si>
     <t>False</t>
+  </si>
+  <si>
+    <t>耐力消耗2点</t>
+  </si>
+  <si>
+    <t>1;6;2;3;1001</t>
   </si>
 </sst>
 </file>
@@ -1145,46 +1148,56 @@
         <v>65</v>
       </c>
       <c r="F4" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+      <c r="L4" s="12">
+        <v>-1</v>
+      </c>
+      <c r="M4" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="12">
+        <v>5</v>
+      </c>
+      <c r="O4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12" t="s">
+      <c r="P4" s="12" t="s">
         <v>67</v>
       </c>
+      <c r="Q4" s="12"/>
       <c r="R4" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X4" s="14"/>
       <c r="Y4" s="9"/>
@@ -1212,19 +1225,19 @@
         <v>70</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -1242,22 +1255,22 @@
         <v>71</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1284,13 +1297,13 @@
         <v>70</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>74</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>70</v>
@@ -1311,19 +1324,19 @@
         <v>77</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
@@ -1347,22 +1360,22 @@
         <v>79</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>81</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K7" s="4">
         <v>0</v>
@@ -1380,13 +1393,13 @@
         <v>77</v>
       </c>
       <c r="P7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="Q7" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="R7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S7" s="4" t="s">
         <v>77</v>
@@ -1423,19 +1436,80 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="B8" s="1">
+        <v>9001</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
     </row>
     <row r="9">
       <c r="B9" s="1"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>3001</t>
+  </si>
+  <si>
+    <t>4001002</t>
   </si>
   <si>
     <t>1;3;3;1;1001</t>
@@ -1225,7 +1228,7 @@
         <v>70</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>65</v>
@@ -1252,7 +1255,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>65</v>
@@ -1288,10 +1291,10 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>70</v>
@@ -1300,7 +1303,7 @@
         <v>65</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>65</v>
@@ -1309,7 +1312,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="12"/>
@@ -1318,10 +1321,10 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S6" s="4" t="s">
         <v>65</v>
@@ -1354,22 +1357,22 @@
         <v>1005</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>65</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>65</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>65</v>
@@ -1390,31 +1393,31 @@
         <v>60</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>67</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>65</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="4">
@@ -1436,13 +1439,13 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1453,7 +1456,7 @@
         <v>63</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>65</v>
@@ -1480,7 +1483,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>65</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DADB8FF-41F2-4366-B0F0-46AE5CE44173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D038149B-CFCD-4209-9BCC-FD3AC8C545EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -428,6 +428,18 @@
   </si>
   <si>
     <t>1;6;2;3;1001</t>
+  </si>
+  <si>
+    <t>自动恢复耐力</t>
+  </si>
+  <si>
+    <t>耐力恢复2点/60帧</t>
+  </si>
+  <si>
+    <t>1;6;2;0;1001</t>
+  </si>
+  <si>
+    <t>1006</t>
   </si>
 </sst>
 </file>
@@ -508,11 +520,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
@@ -853,34 +866,34 @@
   <dimension ref="A1:AG26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="12.21875" customWidth="1" style="4"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1" style="4"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1" style="4"/>
-    <col min="7" max="7" width="25.77734375" customWidth="1" style="4"/>
-    <col min="8" max="8" width="24.88671875" customWidth="1" style="4"/>
-    <col min="9" max="9" width="37" customWidth="1" style="4"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1" style="4"/>
-    <col min="11" max="11" width="12.21875" customWidth="1" style="4"/>
-    <col min="12" max="12" width="12.21875" customWidth="1" style="12"/>
-    <col min="13" max="13" width="21" customWidth="1" style="4"/>
-    <col min="14" max="16" width="14.21875" customWidth="1" style="4"/>
-    <col min="17" max="17" width="15.21875" customWidth="1" style="4"/>
-    <col min="18" max="18" width="15" customWidth="1" style="4"/>
-    <col min="19" max="19" width="15.109375" customWidth="1" style="4"/>
-    <col min="20" max="20" width="13.44140625" customWidth="1" style="4"/>
-    <col min="21" max="21" width="15.21875" customWidth="1" style="4"/>
-    <col min="22" max="22" width="17.77734375" customWidth="1" style="4"/>
-    <col min="23" max="23" width="18.6640625" customWidth="1" style="4"/>
-    <col min="24" max="24" width="24.44140625" customWidth="1" style="4"/>
-    <col min="25" max="25" width="12.21875" customWidth="1" style="4"/>
-    <col min="26" max="26" width="11" customWidth="1" style="4"/>
-    <col min="27" max="27" width="14.77734375" customWidth="1" style="4"/>
-    <col min="28" max="28" width="19.44140625" customWidth="1" style="4"/>
-    <col min="29" max="29" width="15.44140625" customWidth="1" style="4"/>
-    <col min="30" max="30" width="12.21875" customWidth="1" style="4"/>
-    <col min="31" max="31" width="17.33203125" customWidth="1" style="4"/>
-    <col min="32" max="32" width="14.33203125" customWidth="1" style="4"/>
-    <col min="33" max="33" width="13.109375" customWidth="1" style="4"/>
+    <col min="3" max="4" width="12.21875" customWidth="1" style="5"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1" style="5"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1" style="5"/>
+    <col min="7" max="7" width="25.77734375" customWidth="1" style="5"/>
+    <col min="8" max="8" width="24.88671875" customWidth="1" style="5"/>
+    <col min="9" max="9" width="37" customWidth="1" style="5"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1" style="5"/>
+    <col min="11" max="11" width="12.21875" customWidth="1" style="5"/>
+    <col min="12" max="12" width="12.21875" customWidth="1" style="13"/>
+    <col min="13" max="13" width="21" customWidth="1" style="5"/>
+    <col min="14" max="16" width="14.21875" customWidth="1" style="5"/>
+    <col min="17" max="17" width="15.21875" customWidth="1" style="5"/>
+    <col min="18" max="18" width="15" customWidth="1" style="5"/>
+    <col min="19" max="19" width="15.109375" customWidth="1" style="5"/>
+    <col min="20" max="20" width="13.44140625" customWidth="1" style="5"/>
+    <col min="21" max="21" width="15.21875" customWidth="1" style="5"/>
+    <col min="22" max="22" width="17.77734375" customWidth="1" style="5"/>
+    <col min="23" max="23" width="18.6640625" customWidth="1" style="5"/>
+    <col min="24" max="24" width="24.44140625" customWidth="1" style="5"/>
+    <col min="25" max="25" width="12.21875" customWidth="1" style="5"/>
+    <col min="26" max="26" width="11" customWidth="1" style="5"/>
+    <col min="27" max="27" width="14.77734375" customWidth="1" style="5"/>
+    <col min="28" max="28" width="19.44140625" customWidth="1" style="5"/>
+    <col min="29" max="29" width="15.44140625" customWidth="1" style="5"/>
+    <col min="30" max="30" width="12.21875" customWidth="1" style="5"/>
+    <col min="31" max="31" width="17.33203125" customWidth="1" style="5"/>
+    <col min="32" max="32" width="14.33203125" customWidth="1" style="5"/>
+    <col min="33" max="33" width="13.109375" customWidth="1" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2">
@@ -896,69 +909,69 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23" t="s">
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="8" t="s">
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="W1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="13" t="s">
+      <c r="X1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Y1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -973,245 +986,237 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="22"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="22" t="s">
+      <c r="L2" s="23"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="19" t="s">
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="S2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="21" t="s">
+      <c r="Y2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="O3" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="T3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="V3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="W3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="X3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="14" t="s">
+      <c r="Y3" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="14" t="s">
+      <c r="Z3" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="14" t="s">
+      <c r="AA3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="14" t="s">
+      <c r="AB3" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="14" t="s">
+      <c r="AC3" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="AD3" s="14" t="s">
+      <c r="AD3" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="AE3" s="14" t="s">
+      <c r="AE3" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="AF3" s="14" t="s">
+      <c r="AF3" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AG3" s="14" t="s">
+      <c r="AG3" s="15" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10"/>
-      <c r="B4" s="18">
+      <c r="A4" s="11"/>
+      <c r="B4" s="19">
         <v>1001</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="12">
+      <c r="E4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="13">
         <v>0</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="13">
         <v>-1</v>
       </c>
-      <c r="M4" s="12" t="b">
+      <c r="M4" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="N4" s="12">
-        <v>5</v>
-      </c>
-      <c r="O4" s="12" t="s">
+      <c r="N4" s="13">
+        <v>10</v>
+      </c>
+      <c r="O4" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="P4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="S4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="T4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-      <c r="AG4" s="4"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="10"/>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
@@ -1227,224 +1232,194 @@
       <c r="E5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="4">
+      <c r="G5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="5">
         <v>0</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="13">
         <v>-1</v>
       </c>
-      <c r="M5" s="4" t="b">
+      <c r="M5" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="R5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
-      <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
-      <c r="AG5" s="4"/>
+      <c r="R5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="R6" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
-      <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
-      <c r="AG6" s="4"/>
+      <c r="S6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>1005</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="E7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="4">
+      <c r="I7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="5">
         <v>0</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="13">
         <v>600</v>
       </c>
-      <c r="M7" s="4" t="b">
+      <c r="M7" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="5">
         <v>60</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="R7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="S7" s="4" t="s">
+      <c r="R7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="T7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="U7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="V7" s="4" t="s">
+      <c r="V7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4">
+      <c r="Y7" s="5">
         <v>1</v>
       </c>
-      <c r="Z7" s="4">
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
-      <c r="AA7" s="4">
+      <c r="AA7" s="5">
         <v>10</v>
       </c>
-      <c r="AB7" s="4">
+      <c r="AB7" s="5">
         <v>1</v>
       </c>
-      <c r="AC7" s="4">
+      <c r="AC7" s="5">
         <v>1</v>
       </c>
-      <c r="AD7" s="4">
+      <c r="AD7" s="5">
         <v>0</v>
       </c>
-      <c r="AE7" s="4" t="s">
+      <c r="AE7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AF7" s="4" t="s">
+      <c r="AF7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="AG7" s="4" t="s">
+      <c r="AG7" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1452,129 +1427,247 @@
       <c r="B8" s="1">
         <v>9001</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4" t="s">
+      <c r="E8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="R8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
-      <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
-      <c r="AG8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="R8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" s="13" customFormat="1">
+      <c r="A9" s="11"/>
+      <c r="B9" s="19">
+        <v>1006</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
     </row>
     <row r="10">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="B10" s="3">
+        <v>1007</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <v>-1</v>
+      </c>
+      <c r="M10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>60</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
     </row>
     <row r="11">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
     </row>
     <row r="13">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
     </row>
     <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
     </row>
     <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
     </row>
     <row r="22">
       <c r="B22" s="1"/>
@@ -1583,7 +1676,7 @@
       <c r="B23" s="1"/>
     </row>
     <row r="25">
-      <c r="B25" s="5"/>
+      <c r="B25" s="6"/>
     </row>
     <row r="26">
       <c r="B26" s="1"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D038149B-CFCD-4209-9BCC-FD3AC8C545EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,13 +27,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>fangmenglu</author>
     <author>大马鹿</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="Q3" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -125,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -199,10 +198,10 @@
     <t>string</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>(list#sep=;</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -213,7 +212,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=;),int</t>
@@ -222,10 +221,10 @@
     <t>duration?</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>period</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -236,13 +235,13 @@
       </rPr>
       <t>?</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>(list#sep=</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -253,7 +252,7 @@
       </rPr>
       <t>|),modifier</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=|),grantedAbility</t>
@@ -361,7 +360,7 @@
     <t>奔跑耐力消耗</t>
   </si>
   <si>
-    <t>耐力减少2点/5帧</t>
+    <t>耐力减少1点/5帧</t>
   </si>
   <si>
     <t/>
@@ -424,10 +423,10 @@
     <t>False</t>
   </si>
   <si>
-    <t>耐力消耗2点</t>
-  </si>
-  <si>
-    <t>1;6;2;3;1001</t>
+    <t>耐力消耗1点</t>
+  </si>
+  <si>
+    <t>1;6;1;3;1001</t>
   </si>
   <si>
     <t>自动恢复耐力</t>
@@ -445,14 +444,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -496,6 +502,21 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -516,70 +537,69 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -862,41 +882,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG26"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="12.21875" customWidth="1" style="5"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1" style="5"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1" style="5"/>
-    <col min="7" max="7" width="25.77734375" customWidth="1" style="5"/>
-    <col min="8" max="8" width="24.88671875" customWidth="1" style="5"/>
-    <col min="9" max="9" width="37" customWidth="1" style="5"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1" style="5"/>
-    <col min="11" max="11" width="12.21875" customWidth="1" style="5"/>
-    <col min="12" max="12" width="12.21875" customWidth="1" style="13"/>
-    <col min="13" max="13" width="21" customWidth="1" style="5"/>
-    <col min="14" max="16" width="14.21875" customWidth="1" style="5"/>
-    <col min="17" max="17" width="15.21875" customWidth="1" style="5"/>
-    <col min="18" max="18" width="15" customWidth="1" style="5"/>
-    <col min="19" max="19" width="15.109375" customWidth="1" style="5"/>
-    <col min="20" max="20" width="13.44140625" customWidth="1" style="5"/>
-    <col min="21" max="21" width="15.21875" customWidth="1" style="5"/>
-    <col min="22" max="22" width="17.77734375" customWidth="1" style="5"/>
-    <col min="23" max="23" width="18.6640625" customWidth="1" style="5"/>
-    <col min="24" max="24" width="24.44140625" customWidth="1" style="5"/>
-    <col min="25" max="25" width="12.21875" customWidth="1" style="5"/>
-    <col min="26" max="26" width="11" customWidth="1" style="5"/>
-    <col min="27" max="27" width="14.77734375" customWidth="1" style="5"/>
-    <col min="28" max="28" width="19.44140625" customWidth="1" style="5"/>
-    <col min="29" max="29" width="15.44140625" customWidth="1" style="5"/>
-    <col min="30" max="30" width="12.21875" customWidth="1" style="5"/>
-    <col min="31" max="31" width="17.33203125" customWidth="1" style="5"/>
-    <col min="32" max="32" width="14.33203125" customWidth="1" style="5"/>
-    <col min="33" max="33" width="13.109375" customWidth="1" style="5"/>
+    <col min="3" max="4" width="12.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="16.75" style="4" customWidth="1"/>
+    <col min="7" max="7" width="25.75" style="4" customWidth="1"/>
+    <col min="8" max="8" width="24.875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="37" style="4" customWidth="1"/>
+    <col min="10" max="10" width="18.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.25" style="4" customWidth="1"/>
+    <col min="12" max="12" width="12.25" style="12" customWidth="1"/>
+    <col min="13" max="13" width="21" style="4" customWidth="1"/>
+    <col min="14" max="16" width="14.25" style="4" customWidth="1"/>
+    <col min="17" max="17" width="15.25" style="4" customWidth="1"/>
+    <col min="18" max="18" width="15" style="4" customWidth="1"/>
+    <col min="19" max="19" width="15.125" style="4" customWidth="1"/>
+    <col min="20" max="20" width="13.5" style="4" customWidth="1"/>
+    <col min="21" max="21" width="15.25" style="4" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="4" customWidth="1"/>
+    <col min="23" max="23" width="18.625" style="4" customWidth="1"/>
+    <col min="24" max="24" width="24.5" style="4" customWidth="1"/>
+    <col min="25" max="25" width="12.25" style="4" customWidth="1"/>
+    <col min="26" max="26" width="11" style="4" customWidth="1"/>
+    <col min="27" max="27" width="14.75" style="4" customWidth="1"/>
+    <col min="28" max="28" width="19.5" style="4" customWidth="1"/>
+    <col min="29" max="29" width="15.5" style="4" customWidth="1"/>
+    <col min="30" max="30" width="12.25" style="4" customWidth="1"/>
+    <col min="31" max="31" width="17.375" style="4" customWidth="1"/>
+    <col min="32" max="32" width="14.375" style="4" customWidth="1"/>
+    <col min="33" max="33" width="13.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2">
+    <row r="1" spans="1:33" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -909,71 +929,71 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24" t="s">
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="9" t="s">
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="23" t="s">
+      <c r="Y1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
-    </row>
-    <row r="2">
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -986,239 +1006,239 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23" t="s">
+      <c r="L2" s="22"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="20" t="s">
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="20" t="s">
+      <c r="S2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="X2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="22" t="s">
+      <c r="Y2" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="22"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-    </row>
-    <row r="3">
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="Q3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="10" t="s">
+      <c r="T3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="10" t="s">
+      <c r="U3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="10" t="s">
+      <c r="V3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="10" t="s">
+      <c r="W3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="10" t="s">
+      <c r="X3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="15" t="s">
+      <c r="Y3" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="Z3" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AA3" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AB3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="AD3" s="15" t="s">
+      <c r="AD3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="AE3" s="15" t="s">
+      <c r="AE3" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="AF3" s="15" t="s">
+      <c r="AF3" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AG3" s="15" t="s">
+      <c r="AG3" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="11"/>
-      <c r="B4" s="19">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
+      <c r="B4" s="18">
         <v>1001</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="13">
+      <c r="E4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="12">
         <v>0</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <v>-1</v>
       </c>
-      <c r="M4" s="13" t="b">
+      <c r="M4" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="N4" s="13">
-        <v>10</v>
-      </c>
-      <c r="O4" s="13" t="s">
+      <c r="N4" s="12">
+        <v>5</v>
+      </c>
+      <c r="O4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="T4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="10"/>
-    </row>
-    <row r="5">
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="9"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
@@ -1232,457 +1252,430 @@
       <c r="E5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="5">
+      <c r="G5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="4">
         <v>0</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <v>-1</v>
       </c>
-      <c r="M5" s="5" t="b">
+      <c r="M5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="Q5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="R5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4">
+      <c r="R5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B6" s="3">
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="Q6" s="5" t="s">
+      <c r="Q6" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="R6" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="S6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6">
+      <c r="S6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B7" s="5">
         <v>1005</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="5">
+      <c r="I7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="4">
         <v>0</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="12">
         <v>600</v>
       </c>
-      <c r="M7" s="5" t="b">
+      <c r="M7" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="4">
         <v>60</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q7" s="5" t="s">
+      <c r="Q7" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="R7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="S7" s="5" t="s">
+      <c r="R7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="T7" s="5" t="s">
+      <c r="T7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="U7" s="5" t="s">
+      <c r="U7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="V7" s="5" t="s">
+      <c r="V7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="W7" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="Y7" s="4">
         <v>1</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7" s="4">
         <v>0</v>
       </c>
-      <c r="AA7" s="5">
+      <c r="AA7" s="4">
         <v>10</v>
       </c>
-      <c r="AB7" s="5">
+      <c r="AB7" s="4">
         <v>1</v>
       </c>
-      <c r="AC7" s="5">
+      <c r="AC7" s="4">
         <v>1</v>
       </c>
-      <c r="AD7" s="5">
+      <c r="AD7" s="4">
         <v>0</v>
       </c>
-      <c r="AE7" s="5" t="s">
+      <c r="AE7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AF7" s="5" t="s">
+      <c r="AF7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AG7" s="5" t="s">
+      <c r="AG7" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>9001</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q8" s="5" t="s">
+      <c r="E8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="R8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" s="13" customFormat="1">
-      <c r="A9" s="11"/>
-      <c r="B9" s="19">
+      <c r="R8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10"/>
+      <c r="B9" s="18">
         <v>1006</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13" t="s">
+      <c r="E9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="R9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="T9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="U9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="V9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="W9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="3">
+      <c r="R9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="V9" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="W9" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B10" s="2">
         <v>1007</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="5">
+      <c r="E10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="4">
         <v>0</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="12">
         <v>-1</v>
       </c>
-      <c r="M10" s="5" t="b">
+      <c r="M10" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="4">
         <v>60</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="P10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="W10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14">
+      <c r="R10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
     </row>
-    <row r="25">
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="6">
     <mergeCell ref="Y2:AG2"/>
     <mergeCell ref="Y1:AG1"/>
     <mergeCell ref="K2:M2"/>
@@ -1693,7 +1686,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -198,10 +198,10 @@
     <t>string</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>(list#sep=;</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -212,7 +212,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=;),int</t>
@@ -221,10 +221,10 @@
     <t>duration?</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>period</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -235,13 +235,13 @@
       </rPr>
       <t>?</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>(list#sep=</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -252,7 +252,7 @@
       </rPr>
       <t>|),modifier</t>
     </r>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>(list#sep=|),grantedAbility</t>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>4001003</t>
   </si>
   <si>
     <t>9001</t>
@@ -445,20 +448,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -502,21 +498,6 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -537,69 +518,70 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="25">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -886,37 +868,37 @@
   <dimension ref="A1:AG26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="12.25" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.75" style="4" customWidth="1"/>
-    <col min="7" max="7" width="25.75" style="4" customWidth="1"/>
-    <col min="8" max="8" width="24.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="37" style="4" customWidth="1"/>
-    <col min="10" max="10" width="18.875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.25" style="4" customWidth="1"/>
-    <col min="12" max="12" width="12.25" style="12" customWidth="1"/>
-    <col min="13" max="13" width="21" style="4" customWidth="1"/>
-    <col min="14" max="16" width="14.25" style="4" customWidth="1"/>
-    <col min="17" max="17" width="15.25" style="4" customWidth="1"/>
-    <col min="18" max="18" width="15" style="4" customWidth="1"/>
-    <col min="19" max="19" width="15.125" style="4" customWidth="1"/>
-    <col min="20" max="20" width="13.5" style="4" customWidth="1"/>
-    <col min="21" max="21" width="15.25" style="4" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="4" customWidth="1"/>
-    <col min="23" max="23" width="18.625" style="4" customWidth="1"/>
-    <col min="24" max="24" width="24.5" style="4" customWidth="1"/>
-    <col min="25" max="25" width="12.25" style="4" customWidth="1"/>
-    <col min="26" max="26" width="11" style="4" customWidth="1"/>
-    <col min="27" max="27" width="14.75" style="4" customWidth="1"/>
-    <col min="28" max="28" width="19.5" style="4" customWidth="1"/>
-    <col min="29" max="29" width="15.5" style="4" customWidth="1"/>
-    <col min="30" max="30" width="12.25" style="4" customWidth="1"/>
-    <col min="31" max="31" width="17.375" style="4" customWidth="1"/>
-    <col min="32" max="32" width="14.375" style="4" customWidth="1"/>
-    <col min="33" max="33" width="13.125" style="4" customWidth="1"/>
+    <col min="3" max="4" width="12.25" customWidth="1" style="5"/>
+    <col min="5" max="5" width="15.625" customWidth="1" style="5"/>
+    <col min="6" max="6" width="16.75" customWidth="1" style="5"/>
+    <col min="7" max="7" width="25.75" customWidth="1" style="5"/>
+    <col min="8" max="8" width="24.875" customWidth="1" style="5"/>
+    <col min="9" max="9" width="37" customWidth="1" style="5"/>
+    <col min="10" max="10" width="18.875" customWidth="1" style="5"/>
+    <col min="11" max="11" width="12.25" customWidth="1" style="5"/>
+    <col min="12" max="12" width="12.25" customWidth="1" style="13"/>
+    <col min="13" max="13" width="21" customWidth="1" style="5"/>
+    <col min="14" max="16" width="14.25" customWidth="1" style="5"/>
+    <col min="17" max="17" width="15.25" customWidth="1" style="5"/>
+    <col min="18" max="18" width="15" customWidth="1" style="5"/>
+    <col min="19" max="19" width="15.125" customWidth="1" style="5"/>
+    <col min="20" max="20" width="13.5" customWidth="1" style="5"/>
+    <col min="21" max="21" width="15.25" customWidth="1" style="5"/>
+    <col min="22" max="22" width="17.75" customWidth="1" style="5"/>
+    <col min="23" max="23" width="18.625" customWidth="1" style="5"/>
+    <col min="24" max="24" width="24.5" customWidth="1" style="5"/>
+    <col min="25" max="25" width="12.25" customWidth="1" style="5"/>
+    <col min="26" max="26" width="11" customWidth="1" style="5"/>
+    <col min="27" max="27" width="14.75" customWidth="1" style="5"/>
+    <col min="28" max="28" width="19.5" customWidth="1" style="5"/>
+    <col min="29" max="29" width="15.5" customWidth="1" style="5"/>
+    <col min="30" max="30" width="12.25" customWidth="1" style="5"/>
+    <col min="31" max="31" width="17.375" customWidth="1" style="5"/>
+    <col min="32" max="32" width="14.375" customWidth="1" style="5"/>
+    <col min="33" max="33" width="13.125" customWidth="1" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" ht="17.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -929,71 +911,71 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23" t="s">
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="8" t="s">
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="W1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="13" t="s">
+      <c r="X1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Y1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -1006,676 +988,695 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="22"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="22" t="s">
+      <c r="L2" s="23"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="19" t="s">
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="S2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="21" t="s">
+      <c r="Y2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="O3" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="T3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="V3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="W3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="X3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="14" t="s">
+      <c r="Y3" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="14" t="s">
+      <c r="Z3" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="14" t="s">
+      <c r="AA3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="AB3" s="14" t="s">
+      <c r="AB3" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="14" t="s">
+      <c r="AC3" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="AD3" s="14" t="s">
+      <c r="AD3" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="AE3" s="14" t="s">
+      <c r="AE3" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="AF3" s="14" t="s">
+      <c r="AF3" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AG3" s="14" t="s">
+      <c r="AG3" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="18">
+    <row r="4">
+      <c r="A4" s="11"/>
+      <c r="B4" s="19">
         <v>1001</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="12">
+      <c r="E4" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="13">
         <v>0</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="13">
         <v>-1</v>
       </c>
-      <c r="M4" s="12" t="b">
+      <c r="M4" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="13">
         <v>5</v>
       </c>
-      <c r="O4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="P4" s="12" t="s">
+      <c r="O4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="S4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="T4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="9"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="P4" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+    </row>
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
+        <v>-1</v>
+      </c>
+      <c r="M5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
+        <v>600</v>
+      </c>
+      <c r="M7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>60</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="4">
+      <c r="Q7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="T7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="U7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="5">
         <v>0</v>
       </c>
-      <c r="L5" s="12">
-        <v>-1</v>
-      </c>
-      <c r="M5" s="4" t="b">
+      <c r="AA7" s="5">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="5">
         <v>0</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B6" s="3">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B7" s="5">
-        <v>1005</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="AE7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="4">
-        <v>0</v>
-      </c>
-      <c r="L7" s="12">
-        <v>600</v>
-      </c>
-      <c r="M7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4">
-        <v>60</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="W7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="4">
-        <v>10</v>
-      </c>
-      <c r="AB7" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG7" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8">
       <c r="B8" s="1">
         <v>9001</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" s="13" customFormat="1">
+      <c r="A9" s="11"/>
+      <c r="B9" s="19">
+        <v>1006</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3">
+        <v>1007</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <v>-1</v>
+      </c>
+      <c r="M10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>60</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10"/>
-      <c r="B9" s="18">
-        <v>1006</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="S9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="T9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="V9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B10" s="2">
-        <v>1007</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-      <c r="L10" s="12">
-        <v>-1</v>
-      </c>
-      <c r="M10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <v>60</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W10" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14">
       <c r="B14" s="1"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15">
       <c r="B15" s="1"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16">
       <c r="B16" s="1"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17">
       <c r="B17" s="1"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18">
       <c r="B18" s="1"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19">
       <c r="B19" s="1"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20">
       <c r="B20" s="1"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="B23" s="1"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="5"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25">
+      <c r="B25" s="6"/>
+    </row>
+    <row r="26">
       <c r="B26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells>
     <mergeCell ref="Y2:AG2"/>
     <mergeCell ref="Y1:AG1"/>
     <mergeCell ref="K2:M2"/>
@@ -1686,6 +1687,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>